--- a/artfynd/A 27424-2026 artfynd.xlsx
+++ b/artfynd/A 27424-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135278014</v>
       </c>
       <c r="B2" t="n">
-        <v>92262</v>
+        <v>92264</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>135277761</v>
       </c>
       <c r="B4" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>135277865</v>
       </c>
       <c r="B5" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
